--- a/data_member.xlsx
+++ b/data_member.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3bc92dc3d6a3404d/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47A6CD5A-35C8-4BF0-A708-3D0500DE5534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4549C74-40D5-4D0E-875B-B210FA8C8A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
   <si>
     <t>Nama</t>
   </si>
@@ -73,6 +75,15 @@
   </si>
   <si>
     <t>Tidak</t>
+  </si>
+  <si>
+    <t>Eleanor</t>
+  </si>
+  <si>
+    <t>MiReng</t>
+  </si>
+  <si>
+    <t>Squirell</t>
   </si>
 </sst>
 </file>
@@ -680,25 +691,43 @@
       <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="10"/>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="11">
+        <v>46137</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="10"/>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="11">
+        <v>46137</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="10"/>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="11">
+        <v>46137</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="8">
@@ -792,7 +821,7 @@
     <row r="100" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C100">
         <f>SUM(C2:C21)</f>
-        <v>322913</v>
+        <v>461324</v>
       </c>
     </row>
   </sheetData>
